--- a/output/full_scan/batch_seq2_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq2_2026-08-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O157"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1783</v>
+        <v>2382</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>和康生</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>700.3050797938703</v>
+        <v>680.0774229817511</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>41.3</v>
+        <v>313.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.10816630880981</v>
+        <v>44.62220376073688</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11.7116616422351</v>
+        <v>24.1291106232068</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.293570222064583</v>
+        <v>0.8415893322914108</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0480984393093866</v>
+        <v>0.2080707588613357</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2382</v>
+        <v>2362</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>藍天</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>680.0774229817511</v>
+        <v>666.9102118187535</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>313.5</v>
+        <v>46.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>44.62220376073688</v>
+        <v>55.97977859036317</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>24.1291106232068</v>
+        <v>18.02052986657218</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.8415893322914108</v>
+        <v>2.974816591528437</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2080707588613357</v>
+        <v>0.7433454107879386</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2362</v>
+        <v>2375</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>藍天</t>
+          <t>凱美</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>666.9102118187535</v>
+        <v>661.4373080994221</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46.8</v>
+        <v>124</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.97977859036317</v>
+        <v>39.85779444655816</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.02052986657218</v>
+        <v>30.96617828798251</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.974816591528437</v>
+        <v>0.6162229420895357</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.7433454107879386</v>
+        <v>0.3471473949421444</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>2375</v>
+        <v>1612</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>凱美</t>
+          <t>宏泰</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>661.4373080994221</v>
+        <v>659.9530379418545</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>124</v>
+        <v>32.95</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>39.85779444655816</v>
+        <v>56.13080883330208</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.96617828798251</v>
+        <v>39.60476829110283</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6162229420895357</v>
+        <v>2.449673463117235</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3471473949421444</v>
+        <v>0.4078544588004502</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1612</v>
+        <v>2409</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>宏泰</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>659.9530379418545</v>
+        <v>642.9535902340783</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>32.95</v>
+        <v>27</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.13080883330208</v>
+        <v>55.62291528385624</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>39.60476829110283</v>
+        <v>22.07853971822118</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.449673463117235</v>
+        <v>1.14847783985319</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4078544588004502</v>
+        <v>0.1384533028417256</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>2409</v>
+        <v>2397</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>友通</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>642.9535902340783</v>
+        <v>627.2163198287153</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.62291528385624</v>
+        <v>69.49752532610958</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.07853971822118</v>
+        <v>19.3448579225573</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.14847783985319</v>
+        <v>3.321631982871533</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1384533028417256</v>
+        <v>1.376978438877879</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>2397</v>
+        <v>2354</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>友通</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>627.2163198287153</v>
+        <v>626.3156272505933</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>68</v>
+        <v>63.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.49752532610958</v>
+        <v>68.22097035875501</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>19.3448579225573</v>
+        <v>17.86394406484679</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3.321631982871533</v>
+        <v>3.23156272505933</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.376978438877879</v>
+        <v>0.9198876866783424</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>2354</v>
+        <v>1736</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>626.3156272505933</v>
+        <v>614.6301213161314</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>63.1</v>
+        <v>139.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>68.22097035875501</v>
+        <v>56.62455847822405</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.86394406484679</v>
+        <v>23.18738161886526</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.23156272505933</v>
+        <v>2.168038704424756</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.9198876866783424</v>
+        <v>0.4643188001819398</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1736</v>
+        <v>2408</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>喬山</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>614.6301213161314</v>
+        <v>603.7232546694368</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>139.5</v>
+        <v>502</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.62455847822405</v>
+        <v>62.17977825003716</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.18738161886526</v>
+        <v>14.282554085854</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.168038704424756</v>
+        <v>1.16836263033331</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4643188001819398</v>
+        <v>9.533570462325804</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>2408</v>
+        <v>1618</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>603.7232546694368</v>
+        <v>598.7460192926702</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>502</v>
+        <v>40.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>62.17977825003716</v>
+        <v>58.57905661246566</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>14.282554085854</v>
+        <v>17.31699443631883</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.16836263033331</v>
+        <v>3.114277594588462</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>9.533570462325804</v>
+        <v>0.306570910104722</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1618</v>
+        <v>1597</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>直得</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>598.7460192926702</v>
+        <v>596.4393337356687</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>40.5</v>
+        <v>149</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.57905661246566</v>
+        <v>58.91851932909668</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>17.31699443631883</v>
+        <v>18.24769829654167</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.114277594588462</v>
+        <v>1.989239222074071</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.306570910104722</v>
+        <v>4.03090613083042</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1597</v>
+        <v>2332</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>直得</t>
+          <t>友訊</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>596.4393337356687</v>
+        <v>593.8178499250107</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>149</v>
+        <v>23.6</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.91851932909668</v>
+        <v>56.46022383412273</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>18.24769829654167</v>
+        <v>29.73453587054282</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.989239222074071</v>
+        <v>0.7082880620967631</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4.03090613083042</v>
+        <v>-0.185186485527515</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2332</v>
+        <v>2327</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>友訊</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>593.8178499250107</v>
+        <v>583.462265066135</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>23.6</v>
+        <v>573</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.46022383412273</v>
+        <v>40.44113138984503</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.73453587054282</v>
+        <v>34.25849562905145</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7082880620967631</v>
+        <v>0.6532571326559867</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.185186485527515</v>
+        <v>2.371796237166905</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>2327</v>
+        <v>2399</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>映泰</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>583.462265066135</v>
+        <v>580.6502738156066</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>573</v>
+        <v>43.65</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>40.44113138984503</v>
+        <v>55.77111928663778</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>34.25849562905145</v>
+        <v>23.85659882344294</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6532571326559867</v>
+        <v>2.178861177829668</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.371796237166905</v>
+        <v>1.227169529213663</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>2399</v>
+        <v>2388</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>映泰</t>
+          <t>威盛</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>580.6502738156066</v>
+        <v>571.5125923188313</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>43.65</v>
+        <v>80.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.77111928663778</v>
+        <v>58.00021070057338</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23.85659882344294</v>
+        <v>13.97798998372147</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.178861177829668</v>
+        <v>0.6708732393408156</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.227169529213663</v>
+        <v>1.043411509167875</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>2388</v>
+        <v>2413</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>威盛</t>
+          <t>環科</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>571.5125923188313</v>
+        <v>568.239136329351</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>80.7</v>
+        <v>44.85</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>58.00021070057338</v>
+        <v>55.45307369442956</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13.97798998372147</v>
+        <v>31.54438779959797</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6708732393408156</v>
+        <v>1.958705753245946</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.043411509167875</v>
+        <v>0.8953078396509766</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>2413</v>
+        <v>1590</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>環科</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>568.239136329351</v>
+        <v>566.5528631357354</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>44.85</v>
+        <v>1570</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.45307369442956</v>
+        <v>65.5922582944914</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.54438779959797</v>
+        <v>12.12550513599543</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.958705753245946</v>
+        <v>1.255286313573542</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.8953078396509766</v>
+        <v>22.40221050958566</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1590</v>
+        <v>2356</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>566.5528631357354</v>
+        <v>554.7325296534316</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1570</v>
+        <v>66</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>65.5922582944914</v>
+        <v>55.07065841109826</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>12.12550513599543</v>
+        <v>12.643861897635</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.255286313573542</v>
+        <v>0.5548363825343199</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>22.40221050958566</v>
+        <v>0.5977806122072867</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>2356</v>
+        <v>2417</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>圓剛</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>554.7325296534316</v>
+        <v>554.2761902370889</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>66</v>
+        <v>44.55</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.07065841109826</v>
+        <v>58.92406561333242</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>12.643861897635</v>
+        <v>19.15752652681367</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5548363825343199</v>
+        <v>1.991649327378478</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.5977806122072867</v>
+        <v>0.6750253830532527</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>2417</v>
+        <v>2428</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>圓剛</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>554.2761902370889</v>
+        <v>553.5978153435242</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>44.55</v>
+        <v>229</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.92406561333242</v>
+        <v>41.81234871596046</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>19.15752652681367</v>
+        <v>24.71018412101827</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.991649327378478</v>
+        <v>0.3561896995744288</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.6750253830532527</v>
+        <v>0.3036367465589968</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>2428</v>
+        <v>1731</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>美吾華</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>553.5978153435242</v>
+        <v>535.4095848142985</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>229</v>
+        <v>21.15</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>41.81234871596046</v>
+        <v>63.32155170853913</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.71018412101827</v>
+        <v>38.23184231087332</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3561896995744288</v>
+        <v>0.6409584814298451</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3036367465589968</v>
+        <v>0.0961166358992112</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1731</v>
+        <v>1709</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>美吾華</t>
+          <t>和益</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>535.4095848142985</v>
+        <v>528.5243012046443</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>21.15</v>
+        <v>27.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>63.32155170853913</v>
+        <v>60.63326942424381</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>38.23184231087332</v>
+        <v>31.95058636967723</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6409584814298451</v>
+        <v>0.921179573663042</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0961166358992112</v>
+        <v>0.0877304011412065</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1709</v>
+        <v>1714</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>和益</t>
+          <t>和桐</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>528.5243012046443</v>
+        <v>524.6863596797951</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>27.3</v>
+        <v>16.65</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>60.63326942424381</v>
+        <v>56.8261853680556</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.95058636967723</v>
+        <v>17.93930642198811</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.921179573663042</v>
+        <v>1.689409766299008</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0877304011412065</v>
+        <v>0.22398049848107</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1714</v>
+        <v>2301</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>和桐</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>524.6863596797951</v>
+        <v>522.31414445297</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>16.65</v>
+        <v>271.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.8261853680556</v>
+        <v>68.39260114381833</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17.93930642198811</v>
+        <v>18.50265436580039</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.689409766299008</v>
+        <v>0.9404688402721556</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.22398049848107</v>
+        <v>6.748482292817179</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>2301</v>
+        <v>2421</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>522.31414445297</v>
+        <v>521.7302051502671</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>271.5</v>
+        <v>149.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>68.39260114381833</v>
+        <v>59.57393696790749</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>18.50265436580039</v>
+        <v>25.47748370680472</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9404688402721556</v>
+        <v>1.764903435073903</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>6.748482292817179</v>
+        <v>3.234733874152901</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>2421</v>
+        <v>2072</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>世紀風電</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>521.7302051502671</v>
+        <v>520.7381894290265</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>149.5</v>
+        <v>154</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>59.57393696790749</v>
+        <v>51.00053109791766</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.47748370680472</v>
+        <v>7.990017008699959</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.764903435073903</v>
+        <v>0.6696497015402036</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>3.234733874152901</v>
+        <v>1.392617920743307</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>2072</v>
+        <v>2376</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>世紀風電</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>520.7381894290265</v>
+        <v>520.5955332888913</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>154</v>
+        <v>349.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>51.00053109791766</v>
+        <v>56.29035869289896</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7.990017008699959</v>
+        <v>10.98486859535269</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6696497015402036</v>
+        <v>0.8928993423194911</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.392617920743307</v>
+        <v>1.388597240485605</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>2376</v>
+        <v>1815</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>520.5955332888913</v>
+        <v>516.8822251316313</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>349.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.29035869289896</v>
+        <v>55.7023909919469</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10.98486859535269</v>
+        <v>23.35974462919346</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8928993423194911</v>
+        <v>2.632911674944556</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.388597240485605</v>
+        <v>2.728814199247372</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1815</v>
+        <v>2426</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>鼎元</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>516.8822251316313</v>
+        <v>515.9432998616215</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.7023909919469</v>
+        <v>55.72902274207424</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>23.35974462919346</v>
+        <v>17.39559451158103</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.632911674944556</v>
+        <v>1.892754196351459</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>2.728814199247372</v>
+        <v>1.903128122563193</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>2426</v>
+        <v>2383</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鼎元</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>515.9432998616215</v>
+        <v>509.9434634015416</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>5290</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>55.72902274207424</v>
+        <v>55.7914380395189</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17.39559451158103</v>
+        <v>13.59577249591486</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.892754196351459</v>
+        <v>0.7943463401541588</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.903128122563193</v>
+        <v>83.6204641033724</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>2383</v>
+        <v>2374</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>佳能</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>509.9434634015416</v>
+        <v>503.579628988155</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>5290</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.7914380395189</v>
+        <v>56.18152360769771</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13.59577249591486</v>
+        <v>21.85109089434109</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7943463401541588</v>
+        <v>1.298164217707657</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>83.6204641033724</v>
+        <v>0.9960941358119676</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>2374</v>
+        <v>2380</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>佳能</t>
+          <t>虹光</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>503.579628988155</v>
+        <v>501.9536861607998</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>19.1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>56.18152360769771</v>
+        <v>60.7089905871169</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.85109089434109</v>
+        <v>38.56650355807084</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.298164217707657</v>
+        <v>1.21313877878363</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.9960941358119676</v>
+        <v>-0.4308219049709056</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>2380</v>
+        <v>2347</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>虹光</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>501.9536861607998</v>
+        <v>496.4855562391278</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>19.1</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>60.7089905871169</v>
+        <v>53.25428043615664</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>38.56650355807084</v>
+        <v>16.89836131095986</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.21313877878363</v>
+        <v>0.5664016331024284</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.4308219049709056</v>
+        <v>0.6754657656815934</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>2347</v>
+        <v>2305</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>496.4855562391278</v>
+        <v>492.0335848358664</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>29.05</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.25428043615664</v>
+        <v>45.47219440824882</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16.89836131095986</v>
+        <v>20.62178266443657</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5664016331024284</v>
+        <v>1.155280671456726</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.6754657656815934</v>
+        <v>-0.5905985173871864</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>2305</v>
+        <v>1732</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>毛寶</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>492.0335848358664</v>
+        <v>486.0731338085071</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>29.05</v>
+        <v>26.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45.47219440824882</v>
+        <v>51.73788701167214</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.62178266443657</v>
+        <v>30.99513128435152</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.155280671456726</v>
+        <v>0.6389341479375621</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.5905985173871864</v>
+        <v>0.0161033629503359</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1732</v>
+        <v>2377</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>毛寶</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>486.0731338085071</v>
+        <v>475.5276110083168</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>26.8</v>
+        <v>155</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.73788701167214</v>
+        <v>62.22440879114552</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>30.99513128435152</v>
+        <v>19.05680133781008</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6389341479375621</v>
+        <v>0.7298743661239289</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0161033629503359</v>
+        <v>0.7626871634733776</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>2377</v>
+        <v>2317</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>475.5276110083168</v>
+        <v>474.775831138031</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>155</v>
+        <v>264.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>62.22440879114552</v>
+        <v>59.33216946320782</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>19.05680133781008</v>
+        <v>14.17982394706034</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7298743661239289</v>
+        <v>0.6168276048356506</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.7626871634733776</v>
+        <v>2.824756646131323</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>2317</v>
+        <v>1598</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>岱宇</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>474.775831138031</v>
+        <v>472.1732721340261</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>264.5</v>
+        <v>20.35</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>59.33216946320782</v>
+        <v>55.20433009173317</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14.17982394706034</v>
+        <v>20.68907834120535</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6168276048356506</v>
+        <v>0.2514810353097285</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>2.824756646131323</v>
+        <v>0.0534326018389948</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1598</v>
+        <v>1733</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>岱宇</t>
+          <t>五鼎</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>472.1732721340261</v>
+        <v>469.883541912803</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>20.35</v>
+        <v>30.85</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.20433009173317</v>
+        <v>45.75575932697716</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.68907834120535</v>
+        <v>32.14506558729742</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2514810353097285</v>
+        <v>1.726437802396422</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0534326018389948</v>
+        <v>-0.1305161678811972</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1733</v>
+        <v>1762</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>五鼎</t>
+          <t>中化生</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>469.883541912803</v>
+        <v>457.0880871323016</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>30.85</v>
+        <v>36.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45.75575932697716</v>
+        <v>59.18250765936747</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>32.14506558729742</v>
+        <v>25.62898637149108</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.726437802396422</v>
+        <v>2.907715737945358</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.1305161678811972</v>
+        <v>0.3161643858199734</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1762</v>
+        <v>2368</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>中化生</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>457.0880871323016</v>
+        <v>454.5085416016305</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>36.6</v>
+        <v>926</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>59.18250765936747</v>
+        <v>45.16623851710538</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.62898637149108</v>
+        <v>27.99017492632545</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.907715737945358</v>
+        <v>2.381432764250971</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3161643858199734</v>
+        <v>25.63033651267121</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>2368</v>
+        <v>2308</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>454.5085416016305</v>
+        <v>445.287418279425</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>926</v>
+        <v>1815</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45.16623851710538</v>
+        <v>52.38359933107075</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>27.99017492632545</v>
+        <v>30.80455328127263</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.381432764250971</v>
+        <v>0.7374884215949082</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>25.63033651267121</v>
+        <v>20.92784686739196</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>2308</v>
+        <v>2363</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>矽統</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>445.287418279425</v>
+        <v>442.614192424742</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1815</v>
+        <v>54</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.38359933107075</v>
+        <v>45.63284199030874</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>30.80455328127263</v>
+        <v>25.34715496806296</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7374884215949082</v>
+        <v>0.7473713905544103</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>20.92784686739196</v>
+        <v>0.4414580558053163</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>2363</v>
+        <v>2369</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>矽統</t>
+          <t>菱生</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>442.614192424742</v>
+        <v>442.4473245007627</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>54</v>
+        <v>33.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45.63284199030874</v>
+        <v>48.20275646623409</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>25.34715496806296</v>
+        <v>20.46282109359365</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7473713905544103</v>
+        <v>0.4588646419480888</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4414580558053163</v>
+        <v>0.2698690083726953</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>2369</v>
+        <v>2303</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>菱生</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>442.4473245007627</v>
+        <v>441.8606731918873</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>33.6</v>
+        <v>123</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.20275646623409</v>
+        <v>45.23899386996041</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.46282109359365</v>
+        <v>26.91871980660793</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4588646419480888</v>
+        <v>0.8928940689613659</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2698690083726953</v>
+        <v>-0.2889544180144803</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>2303</v>
+        <v>2379</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>441.8606731918873</v>
+        <v>438.5946149415718</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>123</v>
+        <v>758</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45.23899386996041</v>
+        <v>54.12715130270561</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>26.91871980660793</v>
+        <v>14.16265331271312</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8928940689613659</v>
+        <v>0.5567899973581721</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.2889544180144803</v>
+        <v>1.184845684849883</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>2379</v>
+        <v>2402</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>毅嘉</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>438.5946149415718</v>
+        <v>437.1551571129296</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>758</v>
+        <v>55.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.12715130270561</v>
+        <v>44.33184063187424</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.16265331271312</v>
+        <v>27.18750217838165</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5567899973581721</v>
+        <v>0.7078756594702365</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,51 +3485,51 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.184845684849883</v>
+        <v>0.335532875628918</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>2402</v>
+        <v>1589</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>毅嘉</t>
+          <t>永冠-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>437.1551571129296</v>
+        <v>436.2437654589683</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>55.5</v>
+        <v>5.54</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G58" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>44.33184063187424</v>
+        <v>24.03500245974724</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>27.18750217838165</v>
+        <v>38.8675734956761</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7078756594702365</v>
+        <v>4.024376545896833</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,51 +3538,51 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.335532875628918</v>
+        <v>0.0987316714297876</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1589</v>
+        <v>1725</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>永冠-KY</t>
+          <t>元禎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>436.2437654589683</v>
+        <v>430.070093890268</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>5.54</v>
+        <v>30.9</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>24.03500245974724</v>
+        <v>51.90935025618246</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>38.8675734956761</v>
+        <v>20.62388200181877</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4.024376545896833</v>
+        <v>0.6323259436265484</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0987316714297876</v>
+        <v>0.2612463130796589</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, adx_trending, bb_squeeze_breakout, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1802</v>
+        <v>1785</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>光洋科</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>430.3706955178006</v>
+        <v>428.8120210904192</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>54.7</v>
+        <v>118.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,25 +3626,25 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.2895105547851</v>
+        <v>51.65681322156833</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21.26587894633705</v>
+        <v>27.03175858474991</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8945388852243467</v>
+        <v>0.8817457323791004</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.025589359478068</v>
+        <v>2.807851758345705</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1725</v>
+        <v>2316</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>元禎</t>
+          <t>楠梓電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>430.070093890268</v>
+        <v>425.5134980304459</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>30.9</v>
+        <v>163.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.90935025618246</v>
+        <v>49.37811271466805</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.62388200181877</v>
+        <v>20.15585152704185</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6323259436265484</v>
+        <v>0.7534143464281697</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2612463130796589</v>
+        <v>2.079807551447391</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, adx_trending, bb_squeeze_breakout, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1785</v>
+        <v>2344</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>光洋科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>428.8120210904192</v>
+        <v>423.8803646122877</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>118.5</v>
+        <v>179.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.65681322156833</v>
+        <v>56.89404603209706</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.03175858474991</v>
+        <v>18.76507711552976</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8817457323791004</v>
+        <v>1.217870783126613</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>2.807851758345705</v>
+        <v>3.786955850975399</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>2316</v>
+        <v>2439</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>楠梓電</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>425.5134980304459</v>
+        <v>422.2780776364013</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>163.5</v>
+        <v>82.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.37811271466805</v>
+        <v>43.75008304355815</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.15585152704185</v>
+        <v>32.40535323027741</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7534143464281697</v>
+        <v>1.311880899450946</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>2.079807551447391</v>
+        <v>0.114413825849867</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>2344</v>
+        <v>1717</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>423.8803646122877</v>
+        <v>418.8133907610405</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>179.5</v>
+        <v>70</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>56.89404603209706</v>
+        <v>56.74127934845794</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.76507711552976</v>
+        <v>22.51746681302001</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.217870783126613</v>
+        <v>1.242960630897465</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>3.786955850975399</v>
+        <v>1.354924114435881</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>2439</v>
+        <v>1721</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>三晃</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>422.2780776364013</v>
+        <v>417.2933525051425</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>82.3</v>
+        <v>20.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>43.75008304355815</v>
+        <v>44.53178532947511</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>32.40535323027741</v>
+        <v>22.24748337640018</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.311880899450946</v>
+        <v>0.7945256730208117</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.114413825849867</v>
+        <v>0.165346841839836</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1717</v>
+        <v>1734</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>杏輝</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>418.8133907610405</v>
+        <v>416.0935726971608</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>70</v>
+        <v>31.9</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>56.74127934845794</v>
+        <v>46.89586162024288</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.51746681302001</v>
+        <v>20.83327582276777</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.242960630897465</v>
+        <v>0.5088344348730004</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>1.354924114435881</v>
+        <v>-0.041951735621501</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1721</v>
+        <v>2404</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>三晃</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>417.2933525051425</v>
+        <v>415.211866517251</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>20.3</v>
+        <v>1150</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.53178532947511</v>
+        <v>49.63945938975674</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.24748337640018</v>
+        <v>19.05822746153009</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7945256730208117</v>
+        <v>0.5151647169414274</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.165346841839836</v>
+        <v>9.058075492114083</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1734</v>
+        <v>2385</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>杏輝</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>416.0935726971608</v>
+        <v>413.1330185729424</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>31.9</v>
+        <v>103</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.89586162024288</v>
+        <v>41.0216879406524</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20.83327582276777</v>
+        <v>27.97134343696266</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5088344348730004</v>
+        <v>0.655876657590569</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.041951735621501</v>
+        <v>0.429226099741347</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>2404</v>
+        <v>1718</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>中纖</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>415.211866517251</v>
+        <v>408.5739898832583</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1150</v>
+        <v>10.25</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.63945938975674</v>
+        <v>45.16489622255213</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.05822746153009</v>
+        <v>21.72479667998183</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5151647169414274</v>
+        <v>0.8322276718371427</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>9.058075492114083</v>
+        <v>-0.1509493491215952</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>2385</v>
+        <v>2441</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>超豐</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>413.1330185729424</v>
+        <v>408.5662784930698</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>41.0216879406524</v>
+        <v>54.81968881269641</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>27.97134343696266</v>
+        <v>16.43581923943113</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.655876657590569</v>
+        <v>1.531343748888883</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.429226099741347</v>
+        <v>1.548313044145305</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1718</v>
+        <v>2314</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>中纖</t>
+          <t>台揚</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>408.5739898832583</v>
+        <v>396.0640333913512</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>10.25</v>
+        <v>12.05</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45.16489622255213</v>
+        <v>39.1707294352662</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.72479667998183</v>
+        <v>27.81049552571364</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8322276718371427</v>
+        <v>0.5102576493161707</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1509493491215952</v>
+        <v>0.0895966601283878</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>2441</v>
+        <v>1708</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>東鹼</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>408.5662784930698</v>
+        <v>391.8736119328709</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>129</v>
+        <v>49.95</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>54.81968881269641</v>
+        <v>46.86231124734584</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.43581923943113</v>
+        <v>19.21452768686376</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.531343748888883</v>
+        <v>0.7133034339209434</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.548313044145305</v>
+        <v>-0.3609178104025348</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>2314</v>
+        <v>1726</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>台揚</t>
+          <t>永記</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>396.0640333913512</v>
+        <v>381.1844063585203</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>12.05</v>
+        <v>77.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>39.1707294352662</v>
+        <v>47.40593584882104</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>27.81049552571364</v>
+        <v>16.728298150902</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5102576493161707</v>
+        <v>0.5605957299355326</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0895966601283878</v>
+        <v>-0.0128197700387856</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1708</v>
+        <v>1617</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>東鹼</t>
+          <t>榮星</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>391.8736119328709</v>
+        <v>380.278403670052</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>49.95</v>
+        <v>18.95</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.86231124734584</v>
+        <v>50.74046195023409</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.21452768686376</v>
+        <v>22.39710604291814</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7133034339209434</v>
+        <v>0.9576726494373772</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.3609178104025348</v>
+        <v>-0.024161070833341</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1726</v>
+        <v>2390</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>永記</t>
+          <t>云辰</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>381.1844063585203</v>
+        <v>372.8262492332365</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>77.3</v>
+        <v>10.6</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.40593584882104</v>
+        <v>42.42802161459644</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.728298150902</v>
+        <v>24.49144449779044</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5605957299355326</v>
+        <v>0.7441930797604325</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0128197700387856</v>
+        <v>-0.0015951986035331</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1617</v>
+        <v>2432</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>榮星</t>
+          <t>倚天</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>380.278403670052</v>
+        <v>372.1070853238461</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>18.95</v>
+        <v>28.3</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.74046195023409</v>
+        <v>50.36128162339689</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.39710604291814</v>
+        <v>18.31128070807729</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.9576726494373772</v>
+        <v>0.8810349391077033</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.024161070833341</v>
+        <v>-0.0114255573195446</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>2390</v>
+        <v>1702</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>云辰</t>
+          <t>南僑</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>372.8262492332365</v>
+        <v>366.9752464957539</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>10.6</v>
+        <v>33.35</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>42.42802161459644</v>
+        <v>51.63543071105467</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>24.49144449779044</v>
+        <v>21.55270912715061</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7441930797604325</v>
+        <v>0.2854398000703211</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0015951986035331</v>
+        <v>-0.0800425448514112</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>2432</v>
+        <v>2324</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>倚天</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>372.1070853238461</v>
+        <v>366.4448338446642</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>28.3</v>
+        <v>36.3</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.36128162339689</v>
+        <v>51.02262213454589</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.31128070807729</v>
+        <v>11.97905699703595</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8810349391077033</v>
+        <v>0.5952151648034864</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0114255573195446</v>
+        <v>0.0917839601345771</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1702</v>
+        <v>2355</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>南僑</t>
+          <t>敬鵬</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>366.9752464957539</v>
+        <v>361.9364773972493</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>33.35</v>
+        <v>42.05</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.63543071105467</v>
+        <v>45.51692452153758</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.55270912715061</v>
+        <v>42.75819877391457</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2854398000703211</v>
+        <v>0.6799349008087431</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0800425448514112</v>
+        <v>0.7511513878819214</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>2324</v>
+        <v>2352</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>佳世達</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>366.4448338446642</v>
+        <v>360.3790782271163</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>36.3</v>
+        <v>29.6</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.02262213454589</v>
+        <v>50.7638757535099</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11.97905699703595</v>
+        <v>14.14239311216266</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5952151648034864</v>
+        <v>1.24527470922015</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0917839601345771</v>
+        <v>0.0620343666077267</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>2355</v>
+        <v>2360</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>敬鵬</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>361.9364773972493</v>
+        <v>354.8229464705533</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>42.05</v>
+        <v>2030</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.51692452153758</v>
+        <v>50.57245557890162</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>42.75819877391457</v>
+        <v>13.70436694573175</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6799349008087431</v>
+        <v>0.4499539619319643</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.7511513878819214</v>
+        <v>14.41202408003435</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>2352</v>
+        <v>1583</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>佳世達</t>
+          <t>程泰</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>360.3790782271163</v>
+        <v>350.6510146976887</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>29.6</v>
+        <v>49.7</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>50.7638757535099</v>
+        <v>50.07096090981273</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14.14239311216266</v>
+        <v>8.722556885562955</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.24527470922015</v>
+        <v>0.0519146684139564</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0620343666077267</v>
+        <v>0.0143628465509347</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>2360</v>
+        <v>2313</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>354.8229464705533</v>
+        <v>350.4926169209937</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>2030</v>
+        <v>215</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.57245557890162</v>
+        <v>51.62857786641494</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.70436694573175</v>
+        <v>18.89335859134934</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4499539619319643</v>
+        <v>0.9152522672901162</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>14.41202408003435</v>
+        <v>4.673607366454004</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1583</v>
+        <v>2412</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>程泰</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>350.6510146976887</v>
+        <v>349.7112451001051</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>49.7</v>
+        <v>136.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.07096090981273</v>
+        <v>40.74676244801101</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8.722556885562955</v>
+        <v>14.14494824732023</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.0519146684139564</v>
+        <v>0.5221611787588381</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0143628465509347</v>
+        <v>-0.1701561596259908</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>2313</v>
+        <v>2302</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>麗正</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>350.4926169209937</v>
+        <v>347.3726090377431</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>215</v>
+        <v>42.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.62857786641494</v>
+        <v>52.38274504370946</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.89335859134934</v>
+        <v>17.65560125785548</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9152522672901162</v>
+        <v>0.614784366854551</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>4.673607366454004</v>
+        <v>0.3056011392670157</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>2412</v>
+        <v>2345</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>349.7112451001051</v>
+        <v>343.6672303386007</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>136.5</v>
+        <v>2165</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>40.74676244801101</v>
+        <v>45.40041141204432</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.14494824732023</v>
+        <v>17.3897090873101</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5221611787588381</v>
+        <v>0.967055084598166</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1701561596259908</v>
+        <v>16.93133530490425</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>2302</v>
+        <v>2393</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>麗正</t>
+          <t>億光</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>347.3726090377431</v>
+        <v>342.7589199467649</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>42.5</v>
+        <v>62.4</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>52.38274504370946</v>
+        <v>44.19730793913437</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>17.65560125785548</v>
+        <v>26.15599126275686</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.614784366854551</v>
+        <v>0.735683285910767</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.3056011392670157</v>
+        <v>-0.1931309690684215</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>2345</v>
+        <v>2329</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>343.6672303386007</v>
+        <v>340.804135261036</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>2165</v>
+        <v>44.85</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45.40041141204432</v>
+        <v>46.67224498645019</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.3897090873101</v>
+        <v>22.97089389166691</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.967055084598166</v>
+        <v>0.5007428910911816</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>16.93133530490425</v>
+        <v>0.5942460431194716</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>2393</v>
+        <v>1713</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>億光</t>
+          <t>國化</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>342.7589199467649</v>
+        <v>340.4685934923609</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>62.4</v>
+        <v>44</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.19730793913437</v>
+        <v>29.20672820347471</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>26.15599126275686</v>
+        <v>36.9532216800436</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.735683285910767</v>
+        <v>1.401044823836376</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1931309690684215</v>
+        <v>-0.3355440465123763</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>2329</v>
+        <v>2392</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>正崴</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>340.804135261036</v>
+        <v>339.9036686565926</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>44.85</v>
+        <v>37.95</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.67224498645019</v>
+        <v>57.60383763921541</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.97089389166691</v>
+        <v>14.23474652069189</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5007428910911816</v>
+        <v>0.6132758798915784</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.5942460431194716</v>
+        <v>0.4509894108700871</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1713</v>
+        <v>2406</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>國化</t>
+          <t>國碩</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>340.4685934923609</v>
+        <v>335.0509653953802</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>44</v>
+        <v>31.95</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>29.20672820347471</v>
+        <v>46.47676263588798</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>36.9532216800436</v>
+        <v>18.18424458260869</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.401044823836376</v>
+        <v>0.3612708585679575</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.3355440465123763</v>
+        <v>0.1377975350489684</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>2392</v>
+        <v>2312</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>正崴</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>339.9036686565926</v>
+        <v>332.1965448224461</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>37.95</v>
+        <v>32.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>57.60383763921541</v>
+        <v>50.91970350794086</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.23474652069189</v>
+        <v>13.43068341950855</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6132758798915784</v>
+        <v>0.7622604217178595</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.4509894108700871</v>
+        <v>0.2480194190019767</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>2406</v>
+        <v>2328</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>國碩</t>
+          <t>廣宇</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>335.0509653953802</v>
+        <v>329.7082427795183</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>31.95</v>
+        <v>47.05</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.47676263588798</v>
+        <v>53.42142145596692</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>18.18424458260869</v>
+        <v>20.6334455445898</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3612708585679575</v>
+        <v>1.082477386306424</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1377975350489684</v>
+        <v>0.5651197225766369</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1773</v>
+        <v>2330</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>334.3283917452102</v>
+        <v>326.9837341519871</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>162</v>
+        <v>2380</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>48.96492057600671</v>
+        <v>51.3236378663094</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.75844981749162</v>
+        <v>9.443525181529919</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7461849506271528</v>
+        <v>0.4876731189289489</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.4386138163669368</v>
+        <v>4.541900791604018</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>2312</v>
+        <v>1723</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>中碳</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>332.1965448224461</v>
+        <v>325.3344747302948</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>32.5</v>
+        <v>86.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>50.91970350794086</v>
+        <v>53.5431274632163</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.43068341950855</v>
+        <v>12.92300888970381</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7622604217178595</v>
+        <v>0.5593279976486537</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.2480194190019767</v>
+        <v>-0.0538568423752992</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>2328</v>
+        <v>1737</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>廣宇</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>329.7082427795183</v>
+        <v>317.2946216162564</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>47.05</v>
+        <v>31.9</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>53.42142145596692</v>
+        <v>46.73870388731263</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.6334455445898</v>
+        <v>31.49083246771036</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.082477386306424</v>
+        <v>0.6294621616256464</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.5651197225766369</v>
+        <v>-0.0321076468501901</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>2330</v>
+        <v>2337</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>326.9837341519871</v>
+        <v>316.4874943955035</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>2380</v>
+        <v>133.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>51.3236378663094</v>
+        <v>52.9772608113438</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>9.443525181529919</v>
+        <v>18.15754984612137</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4876731189289489</v>
+        <v>1.716481151441137</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>4.541900791604018</v>
+        <v>2.817147686262668</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1723</v>
+        <v>2434</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>中碳</t>
+          <t>統懋</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>325.3344747302948</v>
+        <v>310.0925305478605</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>86.3</v>
+        <v>52.9</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>53.5431274632163</v>
+        <v>45.29013723985903</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.92300888970381</v>
+        <v>24.54615862840931</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5593279976486537</v>
+        <v>0.8327543879753991</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0538568423752992</v>
+        <v>-2.129442744447503</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1737</v>
+        <v>2430</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>臺鹽</t>
+          <t>燦坤</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>317.2946216162564</v>
+        <v>308.4872161253957</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>31.9</v>
+        <v>17.25</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.73870388731263</v>
+        <v>42.6992081844481</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>31.49083246771036</v>
+        <v>29.75701501296277</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6294621616256464</v>
+        <v>0.3351576660976483</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0321076468501901</v>
+        <v>0.0095690719543027</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>2337</v>
+        <v>2321</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>東訊</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>316.4874943955035</v>
+        <v>304.0724670318875</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>133.5</v>
+        <v>0</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>52.9772608113438</v>
+        <v>43.05894448637225</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.15754984612137</v>
+        <v>10.07079441632094</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.716481151441137</v>
+        <v>0.0062840855533361</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>2.817147686262668</v>
+        <v>-0.9720573667384836</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>2434</v>
+        <v>1615</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>統懋</t>
+          <t>大山</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>310.0925305478605</v>
+        <v>300.7990473979411</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>52.9</v>
+        <v>42.25</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.29013723985903</v>
+        <v>36.99104634644257</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>24.54615862840931</v>
+        <v>22.65367890214649</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.8327543879753991</v>
+        <v>0.622881437733983</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-2.129442744447503</v>
+        <v>-0.0743184971309245</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>2430</v>
+        <v>2340</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>燦坤</t>
+          <t>台亞</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>308.4872161253957</v>
+        <v>293.7907617121333</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>17.25</v>
+        <v>31.9</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>42.6992081844481</v>
+        <v>48.49439003485274</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>29.75701501296277</v>
+        <v>17.14457468600657</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3351576660976483</v>
+        <v>1.244177083952184</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0095690719543027</v>
+        <v>0.4916452882550384</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>2321</v>
+        <v>1609</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>東訊</t>
+          <t>大亞</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>304.0724670318875</v>
+        <v>293.7668915651647</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0</v>
+        <v>36.95</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.05894448637225</v>
+        <v>51.88672966440317</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.07079441632094</v>
+        <v>16.8144297567262</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.0062840855533361</v>
+        <v>1.213958456557377</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.9720573667384836</v>
+        <v>0.1856398815161291</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1615</v>
+        <v>1727</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>大山</t>
+          <t>中華化</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>300.7990473979411</v>
+        <v>292.9500534316621</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>42.25</v>
+        <v>76.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>36.99104634644257</v>
+        <v>47.6797911381901</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>22.65367890214649</v>
+        <v>25.19767217268944</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.622881437733983</v>
+        <v>0.8063837229401093</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0743184971309245</v>
+        <v>0.5755420138405825</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>2340</v>
+        <v>2373</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>台亞</t>
+          <t>震旦行</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>293.7907617121333</v>
+        <v>291.3472747727898</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>31.9</v>
+        <v>53.4</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.49439003485274</v>
+        <v>36.8463457257309</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.14457468600657</v>
+        <v>14.65170275902839</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.244177083952184</v>
+        <v>0.2556800285006115</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.4916452882550384</v>
+        <v>0.0777865858820693</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1609</v>
+        <v>1626</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>大亞</t>
+          <t>艾美特-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>293.7668915651647</v>
+        <v>289.7131207301194</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>36.95</v>
+        <v>9.66</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>51.88672966440317</v>
+        <v>39.58297324155699</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.8144297567262</v>
+        <v>20.66804638849966</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.213958456557377</v>
+        <v>0.7260728637338913</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1856398815161291</v>
+        <v>-0.0297744869546388</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1727</v>
+        <v>2440</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>中華化</t>
+          <t>太空梭</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>292.9500534316621</v>
+        <v>289.5932353297353</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>76.5</v>
+        <v>15.85</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.6797911381901</v>
+        <v>49.8944567888107</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>25.19767217268944</v>
+        <v>26.15383114480787</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8063837229401093</v>
+        <v>0.7627856294357939</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.5755420138405825</v>
+        <v>0.0609895338184868</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>2373</v>
+        <v>2420</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>震旦行</t>
+          <t>新巨</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>291.3472747727898</v>
+        <v>285.1767792060347</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>53.4</v>
+        <v>56.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.8463457257309</v>
+        <v>47.55441993493265</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>14.65170275902839</v>
+        <v>24.85945873826503</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.2556800285006115</v>
+        <v>0.8382602374710547</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0777865858820693</v>
+        <v>0.1796543960742185</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1776</v>
+        <v>2414</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>展宇</t>
+          <t>精技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>290.7077302612747</v>
+        <v>282.2134661634911</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>17</v>
+        <v>56.7</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>37.11554680421032</v>
+        <v>47.08340467047632</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>34.30841917840164</v>
+        <v>19.32496497270608</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.7437448977067511</v>
+        <v>0.7893459883918151</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0015895332443354</v>
+        <v>-0.117525561753061</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1626</v>
+        <v>1735</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>艾美特-KY</t>
+          <t>日勝化</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>289.7131207301194</v>
+        <v>281.8002899790707</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>9.66</v>
+        <v>20.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.58297324155699</v>
+        <v>48.7360634213343</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>20.66804638849966</v>
+        <v>24.07113723794111</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7260728637338913</v>
+        <v>0.2586169000117567</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0297744869546388</v>
+        <v>0.2756198809650816</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>2440</v>
+        <v>2433</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>太空梭</t>
+          <t>互盛電</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>289.5932353297353</v>
+        <v>277.5169852536424</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>15.85</v>
+        <v>41.9</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>49.8944567888107</v>
+        <v>42.87756611599197</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>26.15383114480787</v>
+        <v>9.257978527093419</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7627856294357939</v>
+        <v>0.6132379380380558</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0609895338184868</v>
+        <v>0.0840444804723522</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>2420</v>
+        <v>1707</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>新巨</t>
+          <t>葡萄王</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>285.1767792060347</v>
+        <v>276.2833449595103</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>56.5</v>
+        <v>90.3</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.55441993493265</v>
+        <v>43.51059040430472</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24.85945873826503</v>
+        <v>33.09048356614463</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8382602374710547</v>
+        <v>0.5719214884326986</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1796543960742185</v>
+        <v>0.2259341704424093</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>2414</v>
+        <v>2323</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>精技</t>
+          <t>中環</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>282.2134661634911</v>
+        <v>273.3368894859012</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>56.7</v>
+        <v>10.25</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.08340467047632</v>
+        <v>46.28426173636361</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.32496497270608</v>
+        <v>19.00842170087584</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7893459883918151</v>
+        <v>1.023603366211254</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.117525561753061</v>
+        <v>0.0437577426232804</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1735</v>
+        <v>2367</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>日勝化</t>
+          <t>燿華</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>281.8002899790707</v>
+        <v>272.8151947916116</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>20.5</v>
+        <v>44.25</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.7360634213343</v>
+        <v>48.48529888542603</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>24.07113723794111</v>
+        <v>34.31180702613396</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.2586169000117567</v>
+        <v>1.133129942137932</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.2756198809650816</v>
+        <v>1.018554750055964</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>2433</v>
+        <v>1711</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>互盛電</t>
+          <t>永光</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>277.5169852536424</v>
+        <v>270.6545964148596</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>41.9</v>
+        <v>38.05</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>42.87756611599197</v>
+        <v>51.01046053829239</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>9.257978527093419</v>
+        <v>21.59690672958948</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6132379380380558</v>
+        <v>0.5403074593168254</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0840444804723522</v>
+        <v>0.6082799470438678</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1707</v>
+        <v>2342</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>葡萄王</t>
+          <t>茂矽</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>276.2833449595103</v>
+        <v>270.1776068797824</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>90.3</v>
+        <v>37.1</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>43.51059040430472</v>
+        <v>43.29891504312823</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>33.09048356614463</v>
+        <v>27.98584249802138</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5719214884326986</v>
+        <v>0.5422995826439343</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.2259341704424093</v>
+        <v>0.2330354101826599</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>2323</v>
+        <v>1760</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>中環</t>
+          <t>寶齡富錦</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>273.3368894859012</v>
+        <v>268.2817875846389</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>10.25</v>
+        <v>59.3</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.28426173636361</v>
+        <v>44.77768658860786</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>19.00842170087584</v>
+        <v>10.76168956137084</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.023603366211254</v>
+        <v>0.7777280323414291</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0437577426232804</v>
+        <v>-0.06640016996592819</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>2367</v>
+        <v>2349</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>燿華</t>
+          <t>錸德</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>272.8151947916116</v>
+        <v>238.6974135408009</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>44.25</v>
+        <v>11.1</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>48.48529888542603</v>
+        <v>43.34018097017004</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>34.31180702613396</v>
+        <v>34.07764312459843</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.133129942137932</v>
+        <v>0.8200402170566006</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>1.018554750055964</v>
+        <v>0.0954604597142383</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1711</v>
+        <v>1752</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>南光</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>270.6545964148596</v>
+        <v>238.3254323262694</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>38.05</v>
+        <v>31.9</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>51.01046053829239</v>
+        <v>49.23102180390246</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>21.59690672958948</v>
+        <v>12.1866369423577</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5403074593168254</v>
+        <v>1.13447100824247</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.6082799470438678</v>
+        <v>0.079265480724542</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>2342</v>
+        <v>2353</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>茂矽</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>270.1776068797824</v>
+        <v>236.3180874290388</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>37.1</v>
+        <v>31</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>43.29891504312823</v>
+        <v>52.88345875186265</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>27.98584249802138</v>
+        <v>18.29894190731108</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5422995826439343</v>
+        <v>0.7948567509550776</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.2330354101826599</v>
+        <v>0.2947949451115366</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1760</v>
+        <v>1730</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>寶齡富錦</t>
+          <t>花仙子</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>268.2817875846389</v>
+        <v>235.1779654884051</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>59.3</v>
+        <v>51.4</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>44.77768658860786</v>
+        <v>45.90640479898549</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>10.76168956137084</v>
+        <v>23.86634024695527</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.7777280323414291</v>
+        <v>1.160239971281956</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.06640016996592819</v>
+        <v>0.0771004666465491</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1789</v>
+        <v>2331</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>神隆</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>259.8495798969504</v>
+        <v>233.2573767938408</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>18.8</v>
+        <v>19.95</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>39.89723106625773</v>
+        <v>52.08632346318584</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>24.92978783028222</v>
+        <v>20.5809111093419</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.9000281856220649</v>
+        <v>0.7611870142846652</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0733672933574903</v>
+        <v>0.1902594170693468</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1786</v>
+        <v>2431</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>科妍</t>
+          <t>聯昌</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>253.2410858527571</v>
+        <v>233.1134389856781</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>51.8</v>
+        <v>10.2</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>52.80288238639463</v>
+        <v>41.0993802198988</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>23.74263618794384</v>
+        <v>24.7905114312987</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.531681566736353</v>
+        <v>2.232904434787242</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.2907577046327994</v>
+        <v>0.0145072806831491</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>2349</v>
+        <v>1595</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>錸德</t>
+          <t>川寶</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>238.6974135408009</v>
+        <v>229.8121194661935</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>11.1</v>
+        <v>62.6</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.34018097017004</v>
+        <v>51.59318958540973</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>34.07764312459843</v>
+        <v>31.32938589882396</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.8200402170566006</v>
+        <v>0.5605597841082554</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0954604597142383</v>
+        <v>1.856234536775035</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1752</v>
+        <v>2429</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>南光</t>
+          <t>銘旺科</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>238.3254323262694</v>
+        <v>229.3560695283349</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>31.9</v>
+        <v>31.4</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>49.23102180390246</v>
+        <v>36.51905599536538</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12.1866369423577</v>
+        <v>24.84734988710818</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.13447100824247</v>
+        <v>0.2858581063636859</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.079265480724542</v>
+        <v>-0.4127877883433131</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>2353</v>
+        <v>2423</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>固緯</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>236.3180874290388</v>
+        <v>210.5442381511993</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>31</v>
+        <v>72.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>52.88345875186265</v>
+        <v>46.94196493458782</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>18.29894190731108</v>
+        <v>12.15126014702943</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.7948567509550776</v>
+        <v>1.358708735547371</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.2947949451115366</v>
+        <v>0.1826330697907866</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1730</v>
+        <v>1712</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>花仙子</t>
+          <t>興農</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>235.1779654884051</v>
+        <v>210.3722974767694</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>51.4</v>
+        <v>39.35</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45.90640479898549</v>
+        <v>51.07530897348764</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>23.86634024695527</v>
+        <v>16.29485814152402</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.160239971281956</v>
+        <v>0.9878130112466876</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0771004666465491</v>
+        <v>-0.0074884377553215</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>2331</v>
+        <v>2338</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>233.2573767938408</v>
+        <v>207.6813487536088</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>19.95</v>
+        <v>40.1</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>52.08632346318584</v>
+        <v>44.30564863771989</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>20.5809111093419</v>
+        <v>34.22131366467372</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.7611870142846652</v>
+        <v>0.4467347821693095</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.1902594170693468</v>
+        <v>0.3760418958541134</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>2431</v>
+        <v>1604</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>聯昌</t>
+          <t>聲寶</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>233.1134389856781</v>
+        <v>207.6759420677569</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>10.2</v>
+        <v>23.2</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>41.0993802198988</v>
+        <v>46.70547501735784</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>24.7905114312987</v>
+        <v>10.11932746174588</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>2.232904434787242</v>
+        <v>0.258346121356572</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0145072806831491</v>
+        <v>-0.0238211093003403</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1595</v>
+        <v>1603</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>川寶</t>
+          <t>華電</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>229.8121194661935</v>
+        <v>206.892595893828</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>62.6</v>
+        <v>29.25</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>51.59318958540973</v>
+        <v>46.27268003114791</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>31.32938589882396</v>
+        <v>27.83352411002912</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.5605597841082554</v>
+        <v>0.7363709990705715</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>1.856234536775035</v>
+        <v>0.1033065020232657</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>2429</v>
+        <v>2438</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>銘旺科</t>
+          <t>翔耀</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>229.3560695283349</v>
+        <v>205.1923171377262</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>31.4</v>
+        <v>17.5</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>36.51905599536538</v>
+        <v>46.02274314765712</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>24.84734988710818</v>
+        <v>9.041402339387719</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.2858581063636859</v>
+        <v>0.3891478245029575</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.4127877883433131</v>
+        <v>0.1335954927427395</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>2423</v>
+        <v>1720</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>固緯</t>
+          <t>生達</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>210.5442381511993</v>
+        <v>203.719910670645</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>72.5</v>
+        <v>56.7</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>46.94196493458782</v>
+        <v>33.26645480663903</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>12.15126014702943</v>
+        <v>31.69738065317833</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.358708735547371</v>
+        <v>1.181115867633207</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.1826330697907866</v>
+        <v>-0.1571122859926434</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>1712</v>
+        <v>2351</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>興農</t>
+          <t>順德</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>210.3722974767694</v>
+        <v>202.3603139590452</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>39.35</v>
+        <v>168.5</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>51.07530897348764</v>
+        <v>48.71464522365739</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>16.29485814152402</v>
+        <v>19.9138988860818</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.9878130112466876</v>
+        <v>0.779733280187646</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0074884377553215</v>
+        <v>2.765330230981492</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>2338</v>
+        <v>1623</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>大東電</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>207.6813487536088</v>
+        <v>201.8034787242152</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>40.1</v>
+        <v>210</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>44.30564863771989</v>
+        <v>42.35681779749003</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>34.22131366467372</v>
+        <v>12.35944380839626</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.4467347821693095</v>
+        <v>0.4100848222710742</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.3760418958541134</v>
+        <v>-0.7523896343107861</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>1604</v>
+        <v>2401</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>聲寶</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>207.6759420677569</v>
+        <v>198.7406572569143</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>23.2</v>
+        <v>27.95</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>46.70547501735784</v>
+        <v>49.73500469087061</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>10.11932746174588</v>
+        <v>18.9966470178192</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.258346121356572</v>
+        <v>0.4616331291822457</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.0238211093003403</v>
+        <v>0.1898242511753691</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>1603</v>
+        <v>1710</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>華電</t>
+          <t>東聯</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>206.892595893828</v>
+        <v>195.6484034614606</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>29.25</v>
+        <v>14.5</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>46.27268003114791</v>
+        <v>48.28403802892619</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>27.83352411002912</v>
+        <v>15.35217076914257</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.7363709990705715</v>
+        <v>0.5346470126956404</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.1033065020232657</v>
+        <v>-0.085090234712387</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>2438</v>
+        <v>1722</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>翔耀</t>
+          <t>台肥</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>205.1923171377262</v>
+        <v>195.146407912075</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>17.5</v>
+        <v>46.1</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>46.02274314765712</v>
+        <v>47.09681230364932</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>9.041402339387719</v>
+        <v>20.83043908774022</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.3891478245029575</v>
+        <v>0.8716009561273247</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.1335954927427395</v>
+        <v>-0.0226265178020909</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>1720</v>
+        <v>2419</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>生達</t>
+          <t>仲琦</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>203.719910670645</v>
+        <v>190.1371329978683</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>56.7</v>
+        <v>24.95</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>33.26645480663903</v>
+        <v>46.10058785754821</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>31.69738065317833</v>
+        <v>30.24456775233963</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1.181115867633207</v>
+        <v>0.5616656697827689</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.1571122859926434</v>
+        <v>0.2065760051496434</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7788,21 +7788,21 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>2351</v>
+        <v>2415</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>順德</t>
+          <t>錩新</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>202.3603139590452</v>
+        <v>189.3605747126648</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>168.5</v>
+        <v>31</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>48.71464522365739</v>
+        <v>43.28575678998396</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>19.9138988860818</v>
+        <v>18.28640913065249</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.779733280187646</v>
+        <v>0.5407245879722703</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>2.765330230981492</v>
+        <v>-0.1965652738545591</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>1623</v>
+        <v>2424</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>大東電</t>
+          <t>隴華</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>201.8034787242152</v>
+        <v>177.298016094614</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>210</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>42.35681779749003</v>
+        <v>44.53438311940779</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>12.35944380839626</v>
+        <v>29.1924534568715</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.4100848222710742</v>
+        <v>0.5038333341235486</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.7523896343107861</v>
+        <v>0.2186437512691055</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>1795</v>
+        <v>1614</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>美時</t>
+          <t>三洋電</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>199.9654999733201</v>
+        <v>169.6504758944996</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>193.5</v>
+        <v>30.85</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>54.57081418477888</v>
+        <v>40.85589831538017</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>11.0717205298983</v>
+        <v>13.3749390336297</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.9425568086126532</v>
+        <v>1.716855106533826</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>1.320672663005514</v>
+        <v>-0.0133922574501105</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>2401</v>
+        <v>1616</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>198.7406572569143</v>
+        <v>169.1261976940962</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>27.95</v>
+        <v>19.75</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>49.73500469087061</v>
+        <v>45.90891657738107</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>18.9966470178192</v>
+        <v>27.67426382582757</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.4616331291822457</v>
+        <v>0.4914333626642956</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.1898242511753691</v>
+        <v>0.1676368007167716</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>1710</v>
+        <v>2387</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>東聯</t>
+          <t>精元</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>195.6484034614606</v>
+        <v>163.7309755121872</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>14.5</v>
+        <v>37.55</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>48.28403802892619</v>
+        <v>40.49431659791337</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>15.35217076914257</v>
+        <v>15.37287424495172</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.5346470126956404</v>
+        <v>2.047104225283515</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.085090234712387</v>
+        <v>0.0341432392365241</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>1722</v>
+        <v>1611</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>台肥</t>
+          <t>中電</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>195.146407912075</v>
+        <v>162.5944660894266</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>46.1</v>
+        <v>11.85</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>47.09681230364932</v>
+        <v>41.26270409335505</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>20.83043908774022</v>
+        <v>22.310292634391</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.8716009561273247</v>
+        <v>0.8720013428017885</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.0226265178020909</v>
+        <v>0.0214529967485984</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>2419</v>
+        <v>2427</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>仲琦</t>
+          <t>三商電</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>190.1371329978683</v>
+        <v>160.0930192037744</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>24.95</v>
+        <v>21.9</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>46.10058785754821</v>
+        <v>40.20700966745239</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>30.24456775233963</v>
+        <v>17.80826313758281</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.5616656697827689</v>
+        <v>0.2898446236512896</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.2065760051496434</v>
+        <v>-0.1969243650047879</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>2415</v>
+        <v>1587</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>錩新</t>
+          <t>吉茂</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>189.3605747126648</v>
+        <v>152.7500224739749</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>31</v>
+        <v>24.3</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>43.28575678998396</v>
+        <v>38.42858831685182</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>18.28640913065249</v>
+        <v>24.66176999296919</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.5407245879722703</v>
+        <v>0.7147782285567256</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.1965652738545591</v>
+        <v>0.1149038999838013</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>2424</v>
+        <v>2365</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>隴華</t>
+          <t>昆盈</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>177.298016094614</v>
+        <v>141.7913879578339</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>31.25</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,13 +8237,13 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>44.53438311940779</v>
+        <v>53.32513050751162</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>29.1924534568715</v>
+        <v>22.7664829570416</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.5038333341235486</v>
+        <v>0.3866266022615006</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.2186437512691055</v>
+        <v>0.418573709071268</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>1614</v>
+        <v>2405</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>三洋電</t>
+          <t>輔信</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>169.6504758944996</v>
+        <v>130.1657549124498</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>30.85</v>
+        <v>16.35</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,13 +8290,13 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>40.85589831538017</v>
+        <v>48.26981933620237</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>13.3749390336297</v>
+        <v>13.51240967323303</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>1.716855106533826</v>
+        <v>0.5652152003889472</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>0</v>
@@ -8308,486 +8308,9 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.0133922574501105</v>
+        <v>0.09956647586703379</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
-        <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
-        <v>1616</v>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>億泰</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D149" s="2" t="n">
-        <v>169.1261976940962</v>
-      </c>
-      <c r="E149" s="2" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>45.90891657738107</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>27.67426382582757</v>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>0.4914333626642956</v>
-      </c>
-      <c r="K149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M149" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N149" s="2" t="n">
-        <v>0.1676368007167716</v>
-      </c>
-      <c r="O149" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
-        <v>2387</v>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>精元</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D150" s="2" t="n">
-        <v>163.7309755121872</v>
-      </c>
-      <c r="E150" s="2" t="n">
-        <v>37.55</v>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>40.49431659791337</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>15.37287424495172</v>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>2.047104225283515</v>
-      </c>
-      <c r="K150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N150" s="2" t="n">
-        <v>0.0341432392365241</v>
-      </c>
-      <c r="O150" s="2" t="inlineStr">
-        <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>1611</v>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>中電</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D151" s="2" t="n">
-        <v>162.5944660894266</v>
-      </c>
-      <c r="E151" s="2" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>41.26270409335505</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>22.310292634391</v>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>0.8720013428017885</v>
-      </c>
-      <c r="K151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N151" s="2" t="n">
-        <v>0.0214529967485984</v>
-      </c>
-      <c r="O151" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>2427</v>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>三商電</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D152" s="2" t="n">
-        <v>160.0930192037744</v>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>40.20700966745239</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>17.80826313758281</v>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>0.2898446236512896</v>
-      </c>
-      <c r="K152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N152" s="2" t="n">
-        <v>-0.1969243650047879</v>
-      </c>
-      <c r="O152" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
-        <v>1587</v>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>吉茂</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D153" s="2" t="n">
-        <v>152.7500224739749</v>
-      </c>
-      <c r="E153" s="2" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>38.42858831685182</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>24.66176999296919</v>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>0.7147782285567256</v>
-      </c>
-      <c r="K153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N153" s="2" t="n">
-        <v>0.1149038999838013</v>
-      </c>
-      <c r="O153" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
-        <v>2365</v>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>昆盈</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D154" s="2" t="n">
-        <v>141.7913879578339</v>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>53.32513050751162</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>22.7664829570416</v>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>0.3866266022615006</v>
-      </c>
-      <c r="K154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M154" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N154" s="2" t="n">
-        <v>0.418573709071268</v>
-      </c>
-      <c r="O154" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
-        <v>2405</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>輔信</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D155" s="2" t="n">
-        <v>130.1657549124498</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>16.35</v>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>48.26981933620237</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>13.51240967323303</v>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>0.5652152003889472</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M155" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N155" s="2" t="n">
-        <v>0.09956647586703379</v>
-      </c>
-      <c r="O155" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
-        <v>1805</v>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>寶徠</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D156" s="2" t="n">
-        <v>79.10184970568916</v>
-      </c>
-      <c r="E156" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>47.71562017517304</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>15.57812590115068</v>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>0.1965957606356579</v>
-      </c>
-      <c r="K156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M156" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N156" s="2" t="n">
-        <v>0.0110123730089253</v>
-      </c>
-      <c r="O156" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
-        <v>1806</v>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>冠軍</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D157" s="2" t="n">
-        <v>62.12609936832053</v>
-      </c>
-      <c r="E157" s="2" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>44.23179701101508</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>14.51661878428498</v>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>0.294529604799341</v>
-      </c>
-      <c r="K157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N157" s="2" t="n">
-        <v>-0.0145712888549986</v>
-      </c>
-      <c r="O157" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
